--- a/src/static/xlsx/enriched_data.xlsx
+++ b/src/static/xlsx/enriched_data.xlsx
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>8.1</v>
+        <v>8.148999999999999</v>
       </c>
       <c r="J25" t="n">
         <v>6494</v>
@@ -6121,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>7.722</v>
+        <v>7.7</v>
       </c>
       <c r="J54" t="n">
         <v>6950</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>7.028</v>
+        <v>7.027</v>
       </c>
       <c r="J79" t="n">
-        <v>2970</v>
+        <v>2972</v>
       </c>
       <c r="K79" t="n">
         <v>100000000</v>

--- a/src/static/xlsx/enriched_data.xlsx
+++ b/src/static/xlsx/enriched_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y101"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,26 @@
           <t>providers_co</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>imdbVotes</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>imdbRating</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Director_omdb</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Awards_omdb</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -663,6 +683,26 @@
           <t>[{"provider_name": "Disney Plus"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}]</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>529,170</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>James Cameron</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Won 1 Oscar. 76 wins &amp; 153 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -701,7 +741,7 @@
         <v>7.946</v>
       </c>
       <c r="J3" t="n">
-        <v>20654</v>
+        <v>20655</v>
       </c>
       <c r="K3" t="n">
         <v>200000000</v>
@@ -770,6 +810,26 @@
       <c r="Y3" t="inlineStr">
         <is>
           <t>[{"provider_name": "Netflix"}, {"provider_name": "MovistarTV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>939,737</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Jon Watts</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Nominated for 1 Oscar. 35 wins &amp; 71 nominations total</t>
         </is>
       </c>
     </row>
@@ -807,10 +867,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>7.556</v>
+        <v>7.557</v>
       </c>
       <c r="J4" t="n">
-        <v>5713</v>
+        <v>5718</v>
       </c>
       <c r="K4" t="n">
         <v>200000000</v>
@@ -879,6 +939,26 @@
       <c r="Y4" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}]</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>211,354</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Kelsey Mann</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nominated for 1 Oscar. 4 wins &amp; 105 nominations total</t>
         </is>
       </c>
     </row>
@@ -916,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>8.180999999999999</v>
+        <v>8.182</v>
       </c>
       <c r="J5" t="n">
-        <v>9705</v>
+        <v>9708</v>
       </c>
       <c r="K5" t="n">
         <v>170000000</v>
@@ -988,6 +1068,26 @@
       <c r="Y5" t="inlineStr">
         <is>
           <t>[{"provider_name": "Universal+ Amazon Channel"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>754,892</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Joseph Kosinski</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Won 1 Oscar. 111 wins &amp; 238 nominations total</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>6.982</v>
       </c>
       <c r="J6" t="n">
         <v>9750</v>
@@ -1097,6 +1197,26 @@
       <c r="Y6" t="inlineStr">
         <is>
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>596,493</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Greta Gerwig</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Won 1 Oscar. 208 wins &amp; 437 nominations total</t>
         </is>
       </c>
     </row>
@@ -1134,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>7.6</v>
+        <v>7.624</v>
       </c>
       <c r="J7" t="n">
-        <v>9568</v>
+        <v>9569</v>
       </c>
       <c r="K7" t="n">
         <v>100000000</v>
@@ -1206,6 +1326,26 @@
       <c r="Y7" t="inlineStr">
         <is>
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>263,354</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Aaron Horvath, Michael Jelenic, Pierre Leduc</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 48 nominations total</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1386,7 @@
         <v>7.608</v>
       </c>
       <c r="J8" t="n">
-        <v>7000</v>
+        <v>7003</v>
       </c>
       <c r="K8" t="n">
         <v>200000000</v>
@@ -1315,6 +1455,26 @@
       <c r="Y8" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}]</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>480,069</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Shawn Levy</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>18 wins &amp; 53 nominations total</t>
         </is>
       </c>
     </row>
@@ -1352,10 +1512,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>7.108</v>
+        <v>7.104</v>
       </c>
       <c r="J9" t="n">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="K9" t="n">
         <v>150000000</v>
@@ -1424,6 +1584,26 @@
       <c r="Y9" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}]</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>88,419</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>David G. Derrick Jr., Jason Hand, Dana Ledoux Miller</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 25 nominations total</t>
         </is>
       </c>
     </row>
@@ -1535,6 +1715,26 @@
           <t>[{"provider_name": "Netflix"}, {"provider_name": "MovistarTV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>216,826</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Colin Trevorrow</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 win &amp; 26 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1570,10 +1770,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>7.051</v>
+        <v>7.052</v>
       </c>
       <c r="J11" t="n">
-        <v>2668</v>
+        <v>2670</v>
       </c>
       <c r="K11" t="n">
         <v>100000000</v>
@@ -1642,6 +1842,26 @@
       <c r="Y11" t="inlineStr">
         <is>
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>60,760</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Chris Renaud, Patrick Delage</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 3 nominations total</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.264</v>
+        <v>7.3</v>
       </c>
       <c r="J12" t="n">
         <v>9452</v>
@@ -1751,6 +1971,26 @@
       <c r="Y12" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}, {"provider_name": "MovistarTV"}]</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>509,879</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Sam Raimi</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>10 wins &amp; 34 nominations total</t>
         </is>
       </c>
     </row>
@@ -1788,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>8.1</v>
+        <v>8.067</v>
       </c>
       <c r="J13" t="n">
-        <v>10057</v>
+        <v>10058</v>
       </c>
       <c r="K13" t="n">
         <v>100000000</v>
@@ -1856,6 +2096,26 @@
       <c r="Y13" t="inlineStr">
         <is>
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}]</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>860,807</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Christopher Nolan</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Won 7 Oscars. 361 wins &amp; 371 nominations total</t>
         </is>
       </c>
     </row>
@@ -1893,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7.3</v>
+        <v>7.301</v>
       </c>
       <c r="J14" t="n">
-        <v>3699</v>
+        <v>3700</v>
       </c>
       <c r="K14" t="n">
         <v>85000000</v>
@@ -1965,6 +2225,26 @@
       <c r="Y14" t="inlineStr">
         <is>
           <t>[{"provider_name": "Netflix"}, {"provider_name": "MovistarTV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}]</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>97,366</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Kyle Balda, Brad Ableson, Jonathan del Val</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 win &amp; 19 nominations total</t>
         </is>
       </c>
     </row>
@@ -2076,6 +2356,26 @@
           <t>[{"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>4,326</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Kaige Chen, Dante Lam, Hark Tsui</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>33 wins &amp; 38 nominations</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2185,6 +2485,26 @@
           <t>[{"provider_name": "Disney Plus"}, {"provider_name": "MovistarTV"}]</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>326,744</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Ryan Coogler</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Won 1 Oscar. 50 wins &amp; 176 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2294,6 +2614,26 @@
           <t>[{"provider_name": "Disney Plus"}]</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>416,650</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>James Gunn</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Nominated for 1 Oscar. 11 wins &amp; 88 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2387,6 +2727,26 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>3,211</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Ling Jia</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>33 wins &amp; 37 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2496,6 +2856,26 @@
           <t>[{"provider_name": "MovistarTV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}]</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>462,850</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Cary Joji Fukunaga</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Won 1 Oscar. 50 wins &amp; 76 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2534,7 +2914,7 @@
         <v>7.655</v>
       </c>
       <c r="J20" t="n">
-        <v>10785</v>
+        <v>10787</v>
       </c>
       <c r="K20" t="n">
         <v>185000000</v>
@@ -2603,6 +2983,26 @@
       <c r="Y20" t="inlineStr">
         <is>
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "MovistarTV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>855,531</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Matt Reeves</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Nominated for 3 Oscars. 39 wins &amp; 185 nominations total</t>
         </is>
       </c>
     </row>
@@ -2714,6 +3114,26 @@
           <t>[{"provider_name": "Disney Plus"}, {"provider_name": "MovistarTV"}]</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>423,610</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Taika Waititi</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>3 wins &amp; 22 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2749,10 +3169,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>6.933</v>
+        <v>6.934</v>
       </c>
       <c r="J22" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="K22" t="n">
         <v>150000000</v>
@@ -2821,6 +3241,26 @@
       <c r="Y22" t="inlineStr">
         <is>
           <t>[{"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>140,661</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Jon M. Chu</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Won 2 Oscars. 112 wins &amp; 300 nominations total</t>
         </is>
       </c>
     </row>
@@ -2932,6 +3372,26 @@
           <t>[{"provider_name": "MovistarTV"}, {"provider_name": "Universal+ Amazon Channel"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>169,187</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Justin Lin</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 13 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2967,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7.444</v>
+        <v>7.443</v>
       </c>
       <c r="J24" t="n">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="K24" t="n">
         <v>200000000</v>
@@ -3039,6 +3499,26 @@
       <c r="Y24" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}]</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>44,872</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Barry Jenkins</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>15 nominations total</t>
         </is>
       </c>
     </row>
@@ -3150,6 +3630,26 @@
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>610,371</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>Denis Villeneuve</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Won 2 Oscars. 106 wins &amp; 367 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3259,6 +3759,26 @@
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>129,963</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>Louis Leterrier</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 15 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3297,7 +3817,7 @@
         <v>8.345000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>7450</v>
+        <v>7453</v>
       </c>
       <c r="K27" t="n">
         <v>100000000</v>
@@ -3366,6 +3886,26 @@
       <c r="Y27" t="inlineStr">
         <is>
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>434,719</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>Joaquim Dos Santos, Kemp Powers, Justin K. Thompson</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Nominated for 1 Oscar. 106 wins &amp; 165 nominations total</t>
         </is>
       </c>
     </row>
@@ -3465,6 +4005,26 @@
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>2,720</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>Sicheng Chen</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3 wins &amp; 4 nominations</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3558,6 +4118,26 @@
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>3,483</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>Yimou Zhang</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>25 wins &amp; 18 nominations</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3667,6 +4247,26 @@
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>168,112</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>Paul King</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Nominated for 1 BAFTA Award3 wins &amp; 42 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3764,6 +4364,26 @@
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>1,494</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>Hark Tsui, Kaige Chen, Dante Lam</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>13 wins &amp; 17 nominations</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3861,6 +4481,26 @@
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14,673</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>Frant Gwo</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>30 wins &amp; 29 nominations</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3970,6 +4610,26 @@
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>118,442</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>Adam Wingard</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 5 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4075,6 +4735,26 @@
           <t>[{"provider_name": "Disney Plus"}]</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>164,598</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Rob Marshall</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>3 wins &amp; 33 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4110,10 +4790,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>7.533</v>
+        <v>7.5</v>
       </c>
       <c r="J35" t="n">
-        <v>4116</v>
+        <v>4117</v>
       </c>
       <c r="K35" t="n">
         <v>291000000</v>
@@ -4182,6 +4862,26 @@
       <c r="Y35" t="inlineStr">
         <is>
           <t>[{"provider_name": "Netflix"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>275,407</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>Christopher McQuarrie</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Nominated for 2 Oscars. 18 wins &amp; 67 nominations total</t>
         </is>
       </c>
     </row>
@@ -4219,10 +4919,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>7.1</v>
+        <v>7.07</v>
       </c>
       <c r="J36" t="n">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="K36" t="n">
         <v>80000000</v>
@@ -4291,6 +4991,26 @@
       <c r="Y36" t="inlineStr">
         <is>
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>63,858</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>Mike Mitchell, Stephanie Stine</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>9 nominations total</t>
         </is>
       </c>
     </row>
@@ -4328,10 +5048,10 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>8.209</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>4051</v>
+        <v>4052</v>
       </c>
       <c r="K37" t="n">
         <v>15700000</v>
@@ -4400,6 +5120,26 @@
       <c r="Y37" t="inlineStr">
         <is>
           <t>[{"provider_name": "Crunchyroll"}, {"provider_name": "Apple TV"}]</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>80,525</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Haruo Sotozaki</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>6 wins &amp; 6 nominations total</t>
         </is>
       </c>
     </row>
@@ -4437,10 +5177,10 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>6.8</v>
+        <v>6.777</v>
       </c>
       <c r="J38" t="n">
-        <v>10577</v>
+        <v>10578</v>
       </c>
       <c r="K38" t="n">
         <v>110000000</v>
@@ -4509,6 +5249,26 @@
       <c r="Y38" t="inlineStr">
         <is>
           <t>[{"provider_name": "Netflix"}, {"provider_name": "MovistarTV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>275,707</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>Andy Serkis</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>1 win &amp; 6 nominations</t>
         </is>
       </c>
     </row>
@@ -4616,6 +5376,26 @@
           <t>[{"provider_name": "Netflix"}]</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>80,453</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Rajkumar Hirani</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>4 wins &amp; 25 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4651,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>7.618</v>
+        <v>7.6</v>
       </c>
       <c r="J40" t="n">
         <v>4743</v>
@@ -4719,6 +5499,26 @@
       <c r="Y40" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}]</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>147,091</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Peter Sohn</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Nominated for 1 Oscar. 2 wins &amp; 68 nominations total</t>
         </is>
       </c>
     </row>
@@ -4756,10 +5556,10 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>7.8</v>
+        <v>7.764</v>
       </c>
       <c r="J41" t="n">
-        <v>2331</v>
+        <v>2334</v>
       </c>
       <c r="K41" t="n">
         <v>122000000</v>
@@ -4828,6 +5628,26 @@
       <c r="Y41" t="inlineStr">
         <is>
           <t>[{"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>52,320</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>Jeff Fowler</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1 nomination total</t>
         </is>
       </c>
     </row>
@@ -4865,10 +5685,10 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>8.217000000000001</v>
+        <v>8.215999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>8089</v>
+        <v>8090</v>
       </c>
       <c r="K42" t="n">
         <v>90000000</v>
@@ -4937,6 +5757,26 @@
       <c r="Y42" t="inlineStr">
         <is>
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "MovistarTV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>196,926</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Joel Crawford, Januel Mercado</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Nominated for 1 Oscar. 8 wins &amp; 58 nominations total</t>
         </is>
       </c>
     </row>
@@ -5044,6 +5884,26 @@
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}]</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>3,142</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>Ling Jia</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>5 wins &amp; 4 nominations</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5079,10 +5939,10 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>6.786</v>
+        <v>6.785</v>
       </c>
       <c r="J44" t="n">
-        <v>3126</v>
+        <v>3128</v>
       </c>
       <c r="K44" t="n">
         <v>120000000</v>
@@ -5151,6 +6011,26 @@
       <c r="Y44" t="inlineStr">
         <is>
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}]</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>101,954</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>Kelly Marcel</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>5 nominations total</t>
         </is>
       </c>
     </row>
@@ -5262,6 +6142,26 @@
           <t>[{"provider_name": "Disney Plus"}]</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>244,977</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>Peyton Reed</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>14 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5355,6 +6255,26 @@
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>1,048</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>Da-Mo Peng, Fei Yan</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>7 wins &amp; 1 nomination total</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5390,10 +6310,10 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>7.578</v>
+        <v>7.577</v>
       </c>
       <c r="J47" t="n">
-        <v>10152</v>
+        <v>10153</v>
       </c>
       <c r="K47" t="n">
         <v>200000000</v>
@@ -5462,6 +6382,26 @@
       <c r="Y47" t="inlineStr">
         <is>
           <t>[{"provider_name": "Max"}, {"provider_name": "MovistarTV"}, {"provider_name": "DIRECTV GO"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}]</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>253,500</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>Adam Wingard</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>3 wins &amp; 20 nominations total</t>
         </is>
       </c>
     </row>
@@ -5561,6 +6501,26 @@
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>1,136</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>Han Han</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>7 wins &amp; 8 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5666,6 +6626,26 @@
           <t>[{"provider_name": "Claro video"}, {"provider_name": "Paramount+ Amazon Channel"}]</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>7,650</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>Guan Hu</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>27 wins &amp; 40 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5759,6 +6739,26 @@
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>1,895</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>Chiyu Zhang</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>15 wins &amp; 27 nominations</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>6.8</v>
+        <v>6.761</v>
       </c>
       <c r="J51" t="n">
-        <v>3137</v>
+        <v>3139</v>
       </c>
       <c r="K51" t="n">
         <v>310000000</v>
@@ -5866,6 +6866,26 @@
       <c r="Y51" t="inlineStr">
         <is>
           <t>[{"provider_name": "Paramount Plus"}, {"provider_name": "Paramount+ Amazon Channel"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>172,374</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>Ridley Scott</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Nominated for 3 BAFTA 3 wins &amp; 86 nominations total</t>
         </is>
       </c>
     </row>
@@ -5903,7 +6923,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>7.042</v>
+        <v>7</v>
       </c>
       <c r="J52" t="n">
         <v>2421</v>
@@ -5975,6 +6995,26 @@
       <c r="Y52" t="inlineStr">
         <is>
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>136,130</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Tim Burton</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>1 win &amp; 39 nominations total</t>
         </is>
       </c>
     </row>
@@ -6086,6 +7126,26 @@
           <t>[{"provider_name": "Paramount Plus"}, {"provider_name": "Paramount+ Amazon Channel"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>118,145</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>Steven Caple Jr.</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1 win &amp; 11 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6195,6 +7255,26 @@
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>371,573</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>Chad Stahelski</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>37 wins &amp; 49 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6304,6 +7384,26 @@
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>104,911</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>James Wan</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>1 win &amp; 6 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6342,7 +7442,7 @@
         <v>7.524</v>
       </c>
       <c r="J56" t="n">
-        <v>9649</v>
+        <v>9650</v>
       </c>
       <c r="K56" t="n">
         <v>150000000</v>
@@ -6411,6 +7511,26 @@
       <c r="Y56" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}, {"provider_name": "MovistarTV"}]</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>455,465</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>Destin Daniel Cretton</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Nominated for 1 Oscar. 19 wins &amp; 67 nominations total</t>
         </is>
       </c>
     </row>
@@ -6494,6 +7614,10 @@
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6532,7 +7656,7 @@
         <v>7.133</v>
       </c>
       <c r="J58" t="n">
-        <v>8377</v>
+        <v>8378</v>
       </c>
       <c r="K58" t="n">
         <v>90000000</v>
@@ -6601,6 +7725,26 @@
       <c r="Y58" t="inlineStr">
         <is>
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Netflix"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "MovistarTV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>187,812</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>Adil El Arbi, Bilall Fallah</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>3 wins &amp; 15 nominations total</t>
         </is>
       </c>
     </row>
@@ -6638,10 +7782,10 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>7.85</v>
+        <v>7.849</v>
       </c>
       <c r="J59" t="n">
-        <v>4482</v>
+        <v>4483</v>
       </c>
       <c r="K59" t="n">
         <v>85000000</v>
@@ -6710,6 +7854,26 @@
       <c r="Y59" t="inlineStr">
         <is>
           <t>[{"provider_name": "MovistarTV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>94,771</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>Garth Jennings, Christophe Lourdelet</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 21 nominations total</t>
         </is>
       </c>
     </row>
@@ -6750,7 +7914,7 @@
         <v>7.782</v>
       </c>
       <c r="J60" t="n">
-        <v>13377</v>
+        <v>13378</v>
       </c>
       <c r="K60" t="n">
         <v>165000000</v>
@@ -6819,6 +7983,26 @@
       <c r="Y60" t="inlineStr">
         <is>
           <t>[{"provider_name": "Max"}, {"provider_name": "MovistarTV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>940,670</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Denis Villeneuve</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Won 6 Oscars. 177 wins &amp; 303 nominations total</t>
         </is>
       </c>
     </row>
@@ -6930,6 +8114,26 @@
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Max"}, {"provider_name": "MovistarTV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>181,039</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>David Yates</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>7 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6965,10 +8169,10 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>6.9</v>
+        <v>6.915</v>
       </c>
       <c r="J62" t="n">
-        <v>6201</v>
+        <v>6202</v>
       </c>
       <c r="K62" t="n">
         <v>120000000</v>
@@ -7037,6 +8241,26 @@
       <c r="Y62" t="inlineStr">
         <is>
           <t>[{"provider_name": "Netflix"}, {"provider_name": "MovistarTV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>276,786</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Ruben Fleischer</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>5 nominations total</t>
         </is>
       </c>
     </row>
@@ -7148,6 +8372,26 @@
           <t>[{"provider_name": "MovistarTV"}, {"provider_name": "Universal+ Amazon Channel"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>103,840</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>Jeff Fowler</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 3 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7183,10 +8427,10 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>7.384</v>
+        <v>7.383</v>
       </c>
       <c r="J64" t="n">
-        <v>2824</v>
+        <v>2826</v>
       </c>
       <c r="K64" t="n">
         <v>100000000</v>
@@ -7255,6 +8499,26 @@
       <c r="Y64" t="inlineStr">
         <is>
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}]</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>95,215</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Adil El Arbi, Bilall Fallah</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>4 nominations total</t>
         </is>
       </c>
     </row>
@@ -7360,6 +8624,26 @@
       <c r="Y65" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}, {"provider_name": "MovistarTV"}]</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>404,566</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Chloé Zhao</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>7 wins &amp; 25 nominations total</t>
         </is>
       </c>
     </row>
@@ -7443,6 +8727,10 @@
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7552,6 +8840,26 @@
           <t>[{"provider_name": "Disney Plus"}]</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>149,104</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>Wes Ball</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Nominated for 1 Oscar. 4 wins &amp; 59 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7657,6 +8965,26 @@
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Max"}, {"provider_name": "MovistarTV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>289,215</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>Jaume Collet-Serra</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 16 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7750,6 +9078,26 @@
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>Wenxiong Xing, Ru Qian</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>8 wins &amp; 7 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7859,6 +9207,26 @@
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>90,545</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>Ben Wheatley</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>3 wins &amp; 4 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7894,10 +9262,10 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>6.557</v>
+        <v>6.556</v>
       </c>
       <c r="J71" t="n">
-        <v>3607</v>
+        <v>3609</v>
       </c>
       <c r="K71" t="n">
         <v>294700000</v>
@@ -7966,6 +9334,26 @@
       <c r="Y71" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}]</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>213,189</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>James Mangold</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Nominated for 1 Oscar. 7 wins &amp; 35 nominations total</t>
         </is>
       </c>
     </row>
@@ -8073,6 +9461,26 @@
           <t>[{"provider_name": "Disney Plus"}, {"provider_name": "MovistarTV"}]</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>444,449</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>Cate Shortland</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>14 wins &amp; 34 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8111,7 +9519,7 @@
         <v>6.855</v>
       </c>
       <c r="J73" t="n">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="K73" t="n">
         <v>155000000</v>
@@ -8180,6 +9588,26 @@
       <c r="Y73" t="inlineStr">
         <is>
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>150,147</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>Lee Isaac Chung</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>22 nominations total</t>
         </is>
       </c>
     </row>
@@ -8279,6 +9707,26 @@
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>5,451</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>Wuershan</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>43 wins &amp; 44 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8384,6 +9832,26 @@
           <t>[{"provider_name": "Max"}, {"provider_name": "MovistarTV"}, {"provider_name": "DIRECTV GO"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}]</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>622,293</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Christopher Nolan</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Won 1 Oscar. 49 wins &amp; 139 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8419,10 +9887,10 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>7</v>
+        <v>7.05</v>
       </c>
       <c r="J76" t="n">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="K76" t="n">
         <v>25000000</v>
@@ -8487,6 +9955,26 @@
       <c r="Y76" t="inlineStr">
         <is>
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}]</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>72,387</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Justin Baldoni</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>3 nominations total</t>
         </is>
       </c>
     </row>
@@ -8524,10 +10012,10 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>7.2</v>
+        <v>7.21</v>
       </c>
       <c r="J77" t="n">
-        <v>3494</v>
+        <v>3495</v>
       </c>
       <c r="K77" t="n">
         <v>80000000</v>
@@ -8596,6 +10084,26 @@
       <c r="Y77" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}]</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>236,207</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Fede Alvarez</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Nominated for 1 Oscar. 13 wins &amp; 44 nominations total</t>
         </is>
       </c>
     </row>
@@ -8691,6 +10199,26 @@
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>Yimou Zhang</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>23 wins &amp; 23 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8800,6 +10328,26 @@
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>149,978</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>Francis Lawrence</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>7 wins &amp; 27 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8893,6 +10441,26 @@
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>2,870</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Rui Cui, Xiang Liu</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>24 wins &amp; 24 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8928,10 +10496,10 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>8.333</v>
+        <v>8.332000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>4646</v>
+        <v>4649</v>
       </c>
       <c r="K81" t="n">
         <v>78000000</v>
@@ -9000,6 +10568,26 @@
       <c r="Y81" t="inlineStr">
         <is>
           <t>[{"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>151,636</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Chris Sanders</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Nominated for 3 Oscars. 85 wins &amp; 104 nominations total</t>
         </is>
       </c>
     </row>
@@ -9040,7 +10628,7 @@
         <v>7.482</v>
       </c>
       <c r="J82" t="n">
-        <v>9015</v>
+        <v>9016</v>
       </c>
       <c r="K82" t="n">
         <v>110000000</v>
@@ -9109,6 +10697,26 @@
       <c r="Y82" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}, {"provider_name": "MovistarTV"}]</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>451,278</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Shawn Levy</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Nominated for 1 Oscar. 5 wins &amp; 29 nominations total</t>
         </is>
       </c>
     </row>
@@ -9146,10 +10754,10 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>7.927</v>
+        <v>7.926</v>
       </c>
       <c r="J83" t="n">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -9214,6 +10822,26 @@
       <c r="Y83" t="inlineStr">
         <is>
           <t>[{"provider_name": "Netflix"}, {"provider_name": "Crunchyroll"}, {"provider_name": "Crunchyroll Amazon Channel"}]</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>50,293</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>Makoto Shinkai</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>3 wins &amp; 30 nominations total</t>
         </is>
       </c>
     </row>
@@ -9325,6 +10953,26 @@
           <t>[{"provider_name": "Netflix"}, {"provider_name": "Universal+ Amazon Channel"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "MovistarTV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>175,100</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>Jeff Fowler</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>3 wins &amp; 12 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9430,6 +11078,26 @@
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}]</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>37,961</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>Benjamin Renner, Guylo Homsy</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>1 win &amp; 7 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9539,6 +11207,26 @@
           <t>[{"provider_name": "Netflix"}, {"provider_name": "Paramount Plus"}, {"provider_name": "MovistarTV"}, {"provider_name": "Claro video"}, {"provider_name": "Paramount+ Amazon Channel"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "MovistarTV"}]</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>300,909</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>John Krasinski</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Nominated for 1 BAFTA Award14 wins &amp; 44 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9574,10 +11262,10 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>7.483</v>
+        <v>7.484</v>
       </c>
       <c r="J87" t="n">
-        <v>4279</v>
+        <v>4281</v>
       </c>
       <c r="K87" t="n">
         <v>20000000</v>
@@ -9646,6 +11334,26 @@
       <c r="Y87" t="inlineStr">
         <is>
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}]</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>108,367</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>Emma Tammi</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>22 nominations total</t>
         </is>
       </c>
     </row>
@@ -9753,6 +11461,26 @@
           <t>[{"provider_name": "Netflix"}]</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>87,143</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>Hayao Miyazaki</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Won 1 Oscar. 35 wins &amp; 89 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9858,6 +11586,26 @@
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Max"}, {"provider_name": "MovistarTV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "MovistarTV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>247,008</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>Baz Luhrmann</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Nominated for 8 Oscars. 93 wins &amp; 241 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9955,6 +11703,26 @@
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>Lin Yongchang</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>3 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10064,6 +11832,26 @@
           <t>[{"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}]</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>98,104</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>Michael B. Jordan</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>28 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10099,10 +11887,10 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>6.659</v>
+        <v>6.66</v>
       </c>
       <c r="J92" t="n">
-        <v>4473</v>
+        <v>4474</v>
       </c>
       <c r="K92" t="n">
         <v>220000000</v>
@@ -10167,6 +11955,26 @@
       <c r="Y92" t="inlineStr">
         <is>
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>228,881</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>Andy Muschietti</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>5 wins &amp; 7 nominations total</t>
         </is>
       </c>
     </row>
@@ -10278,6 +12086,26 @@
           <t>[{"provider_name": "Amazon Prime Video"}, {"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>68,166</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>Michael Chaves</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>1 win &amp; 12 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10313,10 +12141,10 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>6.739</v>
+        <v>6.738</v>
       </c>
       <c r="J94" t="n">
-        <v>2676</v>
+        <v>2678</v>
       </c>
       <c r="K94" t="n">
         <v>67000000</v>
@@ -10381,6 +12209,26 @@
       <c r="Y94" t="inlineStr">
         <is>
           <t>[{"provider_name": "Netflix"}, {"provider_name": "Paramount Plus Apple TV Channel "}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Claro video"}]</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>130,708</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>Michael Sarnoski</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 9 nominations total</t>
         </is>
       </c>
     </row>
@@ -10418,10 +12266,10 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>8.226000000000001</v>
+        <v>8.227</v>
       </c>
       <c r="J95" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K95" t="n">
         <v>15000000</v>
@@ -10486,6 +12334,26 @@
       <c r="Y95" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}]</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>23,969</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>Sam Wrench</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 9 nominations total</t>
         </is>
       </c>
     </row>
@@ -10597,6 +12465,26 @@
           <t>[{"provider_name": "Disney Plus"}]</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>274,907</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>Jared Bush, Byron Howard, Charise Castro Smith</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Won 1 Oscar. 58 wins &amp; 89 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10706,6 +12594,26 @@
           <t>[{"provider_name": "Netflix"}]</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10,136</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>Takehiko Inoue</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>1 win &amp; 4 nominations</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10744,7 +12652,7 @@
         <v>6.319</v>
       </c>
       <c r="J98" t="n">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="K98" t="n">
         <v>175000000</v>
@@ -10809,6 +12717,26 @@
       <c r="Y98" t="inlineStr">
         <is>
           <t>[{"provider_name": "Disney Plus"}]</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>44,822</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>Chris Buck, Fawn Veerasunthorn</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>1 win &amp; 22 nominations total</t>
         </is>
       </c>
     </row>
@@ -10916,6 +12844,26 @@
           <t>[{"provider_name": "Max"}, {"provider_name": "Google Play Movies"}, {"provider_name": "Apple TV"}, {"provider_name": "Google Play Movies"}]</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>23,572</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>Mark Dindal</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>2 wins &amp; 4 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11009,6 +12957,26 @@
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>2,136</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>Jiangjiang Liu</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>27 wins &amp; 28 nominations total</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11102,6 +13070,26 @@
       <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>1,393</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>Junwei Xie, Jing Zou</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>22 wins &amp; 12 nominations total</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/src/static/xlsx/enriched_data.xlsx
+++ b/src/static/xlsx/enriched_data.xlsx
@@ -1128,7 +1128,7 @@
         <v>6.982</v>
       </c>
       <c r="J6" t="n">
-        <v>9750</v>
+        <v>9751</v>
       </c>
       <c r="K6" t="n">
         <v>145000000</v>
@@ -3556,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>8.148999999999999</v>
+        <v>8.148</v>
       </c>
       <c r="J25" t="n">
-        <v>6494</v>
+        <v>6498</v>
       </c>
       <c r="K25" t="n">
         <v>190000000</v>
@@ -8769,7 +8769,7 @@
         <v>7.082</v>
       </c>
       <c r="J67" t="n">
-        <v>3655</v>
+        <v>3657</v>
       </c>
       <c r="K67" t="n">
         <v>160000000</v>
@@ -9765,7 +9765,7 @@
         <v>7.182</v>
       </c>
       <c r="J75" t="n">
-        <v>10165</v>
+        <v>10166</v>
       </c>
       <c r="K75" t="n">
         <v>205000000</v>
@@ -12394,7 +12394,7 @@
         <v>7.595</v>
       </c>
       <c r="J96" t="n">
-        <v>9665</v>
+        <v>9669</v>
       </c>
       <c r="K96" t="n">
         <v>135000000</v>

--- a/src/static/xlsx/enriched_data.xlsx
+++ b/src/static/xlsx/enriched_data.xlsx
@@ -870,7 +870,7 @@
         <v>7.557</v>
       </c>
       <c r="J4" t="n">
-        <v>5718</v>
+        <v>5720</v>
       </c>
       <c r="K4" t="n">
         <v>200000000</v>
@@ -996,10 +996,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>8.182</v>
+        <v>8.180999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>9708</v>
+        <v>9709</v>
       </c>
       <c r="K5" t="n">
         <v>170000000</v>
@@ -1257,7 +1257,7 @@
         <v>7.624</v>
       </c>
       <c r="J7" t="n">
-        <v>9569</v>
+        <v>9570</v>
       </c>
       <c r="K7" t="n">
         <v>100000000</v>
@@ -1386,7 +1386,7 @@
         <v>7.608</v>
       </c>
       <c r="J8" t="n">
-        <v>7003</v>
+        <v>7005</v>
       </c>
       <c r="K8" t="n">
         <v>200000000</v>
@@ -1512,10 +1512,10 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>7.104</v>
+        <v>7.082</v>
       </c>
       <c r="J9" t="n">
-        <v>2141</v>
+        <v>2155</v>
       </c>
       <c r="K9" t="n">
         <v>150000000</v>
@@ -1641,10 +1641,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6.7</v>
+        <v>6.668</v>
       </c>
       <c r="J10" t="n">
-        <v>6303</v>
+        <v>6304</v>
       </c>
       <c r="K10" t="n">
         <v>165000000</v>
@@ -1770,10 +1770,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>7.052</v>
+        <v>7.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="K11" t="n">
         <v>100000000</v>
@@ -1899,10 +1899,10 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.3</v>
+        <v>7.264</v>
       </c>
       <c r="J12" t="n">
-        <v>9452</v>
+        <v>9453</v>
       </c>
       <c r="K12" t="n">
         <v>200000000</v>
@@ -2543,7 +2543,7 @@
         <v>7.948</v>
       </c>
       <c r="J17" t="n">
-        <v>7242</v>
+        <v>7243</v>
       </c>
       <c r="K17" t="n">
         <v>250000000</v>
@@ -3040,10 +3040,10 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>6.42</v>
+        <v>6.421</v>
       </c>
       <c r="J21" t="n">
-        <v>7836</v>
+        <v>7837</v>
       </c>
       <c r="K21" t="n">
         <v>250000000</v>
@@ -3169,10 +3169,10 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>6.934</v>
+        <v>6.931</v>
       </c>
       <c r="J22" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="K22" t="n">
         <v>150000000</v>
@@ -3427,10 +3427,10 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>7.443</v>
+        <v>7.415</v>
       </c>
       <c r="J24" t="n">
-        <v>1864</v>
+        <v>1877</v>
       </c>
       <c r="K24" t="n">
         <v>200000000</v>
@@ -3685,10 +3685,10 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>7.049</v>
+        <v>7.048</v>
       </c>
       <c r="J26" t="n">
-        <v>5834</v>
+        <v>5835</v>
       </c>
       <c r="K26" t="n">
         <v>340000000</v>
@@ -4173,10 +4173,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.086</v>
+        <v>7.085</v>
       </c>
       <c r="J30" t="n">
-        <v>3823</v>
+        <v>3825</v>
       </c>
       <c r="K30" t="n">
         <v>125000000</v>
@@ -4536,10 +4536,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>7.1</v>
+        <v>7.098</v>
       </c>
       <c r="J33" t="n">
-        <v>4132</v>
+        <v>4133</v>
       </c>
       <c r="K33" t="n">
         <v>150000000</v>
@@ -4790,10 +4790,10 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>7.5</v>
+        <v>7.534</v>
       </c>
       <c r="J35" t="n">
-        <v>4117</v>
+        <v>4118</v>
       </c>
       <c r="K35" t="n">
         <v>291000000</v>
@@ -5180,7 +5180,7 @@
         <v>6.777</v>
       </c>
       <c r="J38" t="n">
-        <v>10578</v>
+        <v>10579</v>
       </c>
       <c r="K38" t="n">
         <v>110000000</v>
@@ -5556,10 +5556,10 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>7.764</v>
+        <v>7.8</v>
       </c>
       <c r="J41" t="n">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="K41" t="n">
         <v>122000000</v>
@@ -5688,7 +5688,7 @@
         <v>8.215999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>8090</v>
+        <v>8091</v>
       </c>
       <c r="K42" t="n">
         <v>90000000</v>
@@ -5939,10 +5939,10 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>6.785</v>
+        <v>6.786</v>
       </c>
       <c r="J44" t="n">
-        <v>3128</v>
+        <v>3132</v>
       </c>
       <c r="K44" t="n">
         <v>120000000</v>
@@ -6071,7 +6071,7 @@
         <v>6.294</v>
       </c>
       <c r="J45" t="n">
-        <v>5212</v>
+        <v>5213</v>
       </c>
       <c r="K45" t="n">
         <v>388369742</v>
@@ -6797,7 +6797,7 @@
         <v>6.761</v>
       </c>
       <c r="J51" t="n">
-        <v>3139</v>
+        <v>3141</v>
       </c>
       <c r="K51" t="n">
         <v>310000000</v>
@@ -6923,10 +6923,10 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>7.041</v>
       </c>
       <c r="J52" t="n">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="K52" t="n">
         <v>100000000</v>
@@ -7181,10 +7181,10 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>7.7</v>
+        <v>7.722</v>
       </c>
       <c r="J54" t="n">
-        <v>6950</v>
+        <v>6952</v>
       </c>
       <c r="K54" t="n">
         <v>90000000</v>
@@ -7442,7 +7442,7 @@
         <v>7.524</v>
       </c>
       <c r="J56" t="n">
-        <v>9650</v>
+        <v>9651</v>
       </c>
       <c r="K56" t="n">
         <v>150000000</v>
@@ -7914,7 +7914,7 @@
         <v>7.782</v>
       </c>
       <c r="J60" t="n">
-        <v>13378</v>
+        <v>13380</v>
       </c>
       <c r="K60" t="n">
         <v>165000000</v>
@@ -8301,7 +8301,7 @@
         <v>7.47</v>
       </c>
       <c r="J63" t="n">
-        <v>5431</v>
+        <v>5432</v>
       </c>
       <c r="K63" t="n">
         <v>110000000</v>
@@ -8430,7 +8430,7 @@
         <v>7.383</v>
       </c>
       <c r="J64" t="n">
-        <v>2826</v>
+        <v>2829</v>
       </c>
       <c r="K64" t="n">
         <v>100000000</v>
@@ -9391,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>7.209</v>
+        <v>7.2</v>
       </c>
       <c r="J72" t="n">
         <v>10423</v>
@@ -9519,7 +9519,7 @@
         <v>6.855</v>
       </c>
       <c r="J73" t="n">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="K73" t="n">
         <v>155000000</v>
@@ -9887,10 +9887,10 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>7.05</v>
+        <v>7.049</v>
       </c>
       <c r="J76" t="n">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="K76" t="n">
         <v>25000000</v>
@@ -10496,10 +10496,10 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>8.332000000000001</v>
+        <v>8.333</v>
       </c>
       <c r="J81" t="n">
-        <v>4649</v>
+        <v>4653</v>
       </c>
       <c r="K81" t="n">
         <v>78000000</v>
@@ -11136,7 +11136,7 @@
         <v>7.473</v>
       </c>
       <c r="J86" t="n">
-        <v>6738</v>
+        <v>6739</v>
       </c>
       <c r="K86" t="n">
         <v>55000000</v>
@@ -11265,7 +11265,7 @@
         <v>7.484</v>
       </c>
       <c r="J87" t="n">
-        <v>4281</v>
+        <v>4282</v>
       </c>
       <c r="K87" t="n">
         <v>20000000</v>
@@ -11391,10 +11391,10 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>7.453</v>
+        <v>7.454</v>
       </c>
       <c r="J88" t="n">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="K88" t="n">
         <v>50000000</v>
@@ -11761,7 +11761,7 @@
         <v>7.115</v>
       </c>
       <c r="J91" t="n">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="K91" t="n">
         <v>75000000</v>
@@ -12012,10 +12012,10 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>6.712</v>
+        <v>6.713</v>
       </c>
       <c r="J93" t="n">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="K93" t="n">
         <v>38500000</v>
@@ -12141,10 +12141,10 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>6.738</v>
+        <v>6.739</v>
       </c>
       <c r="J94" t="n">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="K94" t="n">
         <v>67000000</v>

--- a/src/static/xlsx/enriched_data.xlsx
+++ b/src/static/xlsx/enriched_data.xlsx
@@ -2153,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>7.301</v>
+        <v>7.302</v>
       </c>
       <c r="J14" t="n">
-        <v>3700</v>
+        <v>3701</v>
       </c>
       <c r="K14" t="n">
         <v>85000000</v>
